--- a/Formulas & Functions/Date-and-Time-Functions/9_Date_Time_Functions_solution.xlsx
+++ b/Formulas & Functions/Date-and-Time-Functions/9_Date_Time_Functions_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Date-and-Time-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8EAAC7-8F1A-4A32-9928-F8F66B94F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBDC6EE-145D-41D1-89C9-F6A0915CEF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="96">
   <si>
     <t>Email</t>
   </si>
@@ -1904,7 +1926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B5E7F13-C613-4452-9CDB-2C26D6876D9D}">
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="1"/>
@@ -1926,7 +1948,7 @@
     <col min="26" max="26" width="8.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
@@ -1985,11 +2007,14 @@
       <c r="Y1" s="15" t="s">
         <v>95</v>
       </c>
+      <c r="Z1" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="AA1" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>65</v>
       </c>
@@ -2050,9 +2075,28 @@
         <f>SECOND(D2)</f>
         <v>15</v>
       </c>
-      <c r="X2" s="13"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X2" s="13">
+        <f>TIME(T2,U2,V2)</f>
+        <v>0.64045138888888886</v>
+      </c>
+      <c r="Y2" t="str">
+        <f>TEXT(D2,"hh:mm am/pm")</f>
+        <v>03:22 PM</v>
+      </c>
+      <c r="Z2" cm="1">
+        <f t="array" ref="Z2:Z21">HOUR(D2:D21)</f>
+        <v>15</v>
+      </c>
+      <c r="AA2" cm="1">
+        <f t="array" ref="AA2:AA25">_xlfn.SEQUENCE(24,1,1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <f>COUNTIF(_xlfn.ANCHORARRAY($Z$2),AA2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>64</v>
       </c>
@@ -2113,9 +2157,26 @@
         <f t="shared" ref="V3:V21" si="8">SECOND(D3)</f>
         <v>32</v>
       </c>
-      <c r="X3" s="13"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X3" s="13">
+        <f t="shared" ref="X3:X21" si="9">TIME(T3,U3,V3)</f>
+        <v>0.40662037037037035</v>
+      </c>
+      <c r="Y3" t="str">
+        <f t="shared" ref="Y3:Y21" si="10">TEXT(D3,"hh:mm am/pm")</f>
+        <v>09:45 AM</v>
+      </c>
+      <c r="Z3">
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <v>2</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" ref="AB3:AB25" si="11">COUNTIF(_xlfn.ANCHORARRAY($Z$2),AA3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>66</v>
       </c>
@@ -2176,9 +2237,26 @@
         <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="X4" s="13"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X4" s="13">
+        <f t="shared" si="9"/>
+        <v>0.72971064814814823</v>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" si="10"/>
+        <v>05:30 PM</v>
+      </c>
+      <c r="Z4">
+        <v>17</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -2239,9 +2317,26 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="X5" s="13"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X5" s="13">
+        <f t="shared" si="9"/>
+        <v>0.3021875</v>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="10"/>
+        <v>07:15 AM</v>
+      </c>
+      <c r="Z5">
+        <v>7</v>
+      </c>
+      <c r="AA5">
+        <v>4</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>68</v>
       </c>
@@ -2302,9 +2397,26 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="X6" s="13"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X6" s="13">
+        <f t="shared" si="9"/>
+        <v>0.70857638888888885</v>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="10"/>
+        <v>05:00 PM</v>
+      </c>
+      <c r="Z6">
+        <v>17</v>
+      </c>
+      <c r="AA6">
+        <v>5</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>69</v>
       </c>
@@ -2365,9 +2477,26 @@
         <f t="shared" si="8"/>
         <v>58</v>
       </c>
-      <c r="X7" s="13"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X7" s="13">
+        <f t="shared" si="9"/>
+        <v>0.53192129629629636</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="10"/>
+        <v>12:45 PM</v>
+      </c>
+      <c r="Z7">
+        <v>12</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2428,9 +2557,26 @@
         <f t="shared" si="8"/>
         <v>33</v>
       </c>
-      <c r="X8" s="13"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X8" s="13">
+        <f t="shared" si="9"/>
+        <v>0.68788194444444439</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="10"/>
+        <v>04:30 PM</v>
+      </c>
+      <c r="Z8">
+        <v>16</v>
+      </c>
+      <c r="AA8">
+        <v>7</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>71</v>
       </c>
@@ -2491,9 +2637,26 @@
         <f t="shared" si="8"/>
         <v>46</v>
       </c>
-      <c r="X9" s="13"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X9" s="13">
+        <f t="shared" si="9"/>
+        <v>0.34081018518518519</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="10"/>
+        <v>08:10 AM</v>
+      </c>
+      <c r="Z9">
+        <v>8</v>
+      </c>
+      <c r="AA9">
+        <v>8</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>72</v>
       </c>
@@ -2554,9 +2717,26 @@
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="X10" s="13"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X10" s="13">
+        <f t="shared" si="9"/>
+        <v>0.74333333333333329</v>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="10"/>
+        <v>05:50 PM</v>
+      </c>
+      <c r="Z10">
+        <v>17</v>
+      </c>
+      <c r="AA10">
+        <v>9</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -2617,9 +2797,26 @@
         <f t="shared" si="8"/>
         <v>36</v>
       </c>
-      <c r="X11" s="13"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X11" s="13">
+        <f t="shared" si="9"/>
+        <v>0.60805555555555557</v>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="10"/>
+        <v>02:35 PM</v>
+      </c>
+      <c r="Z11">
+        <v>14</v>
+      </c>
+      <c r="AA11">
+        <v>10</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>74</v>
       </c>
@@ -2680,9 +2877,26 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="X12" s="13"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X12" s="13">
+        <f t="shared" si="9"/>
+        <v>0.28493055555555552</v>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="10"/>
+        <v>06:50 AM</v>
+      </c>
+      <c r="Z12">
+        <v>6</v>
+      </c>
+      <c r="AA12">
+        <v>11</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -2743,9 +2957,26 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="X13" s="13"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X13" s="13">
+        <f t="shared" si="9"/>
+        <v>0.55214120370370368</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="10"/>
+        <v>01:15 PM</v>
+      </c>
+      <c r="Z13">
+        <v>13</v>
+      </c>
+      <c r="AA13">
+        <v>12</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>76</v>
       </c>
@@ -2806,9 +3037,26 @@
         <f t="shared" si="8"/>
         <v>39</v>
       </c>
-      <c r="X14" s="13"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X14" s="13">
+        <f t="shared" si="9"/>
+        <v>0.49003472222222227</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="10"/>
+        <v>11:45 AM</v>
+      </c>
+      <c r="Z14">
+        <v>11</v>
+      </c>
+      <c r="AA14">
+        <v>13</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>77</v>
       </c>
@@ -2869,9 +3117,26 @@
         <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="X15" s="13"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="X15" s="13">
+        <f t="shared" si="9"/>
+        <v>0.41725694444444444</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="10"/>
+        <v>10:00 AM</v>
+      </c>
+      <c r="Z15">
+        <v>10</v>
+      </c>
+      <c r="AA15">
+        <v>14</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>78</v>
       </c>
@@ -2932,9 +3197,26 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="X16" s="13"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="X16" s="13">
+        <f t="shared" si="9"/>
+        <v>0.72932870370370362</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="10"/>
+        <v>05:30 PM</v>
+      </c>
+      <c r="Z16">
+        <v>17</v>
+      </c>
+      <c r="AA16">
+        <v>15</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
         <v>79</v>
       </c>
@@ -2995,9 +3277,26 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="X17" s="13"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="X17" s="13">
+        <f t="shared" si="9"/>
+        <v>0.3197800925925926</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="10"/>
+        <v>07:40 AM</v>
+      </c>
+      <c r="Z17">
+        <v>7</v>
+      </c>
+      <c r="AA17">
+        <v>16</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
         <v>80</v>
       </c>
@@ -3058,9 +3357,26 @@
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-      <c r="X18" s="13"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="X18" s="13">
+        <f t="shared" si="9"/>
+        <v>0.71923611111111108</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="10"/>
+        <v>05:15 PM</v>
+      </c>
+      <c r="Z18">
+        <v>17</v>
+      </c>
+      <c r="AA18">
+        <v>17</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
@@ -3121,9 +3437,26 @@
         <f t="shared" si="8"/>
         <v>57</v>
       </c>
-      <c r="X19" s="13"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="X19" s="13">
+        <f t="shared" si="9"/>
+        <v>0.72635416666666675</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="10"/>
+        <v>05:25 PM</v>
+      </c>
+      <c r="Z19">
+        <v>17</v>
+      </c>
+      <c r="AA19">
+        <v>18</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>82</v>
       </c>
@@ -3184,9 +3517,26 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="X20" s="13"/>
-    </row>
-    <row r="21" spans="1:24" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="X20" s="13">
+        <f t="shared" si="9"/>
+        <v>0.29170138888888891</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="10"/>
+        <v>07:00 AM</v>
+      </c>
+      <c r="Z20">
+        <v>7</v>
+      </c>
+      <c r="AA20">
+        <v>19</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A21" s="5" t="s">
         <v>83</v>
       </c>
@@ -3247,7 +3597,60 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="X21" s="13"/>
+      <c r="X21" s="13">
+        <f t="shared" si="9"/>
+        <v>0.73988425925925927</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="10"/>
+        <v>05:45 PM</v>
+      </c>
+      <c r="Z21">
+        <v>17</v>
+      </c>
+      <c r="AA21">
+        <v>20</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA22">
+        <v>21</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA23">
+        <v>22</v>
+      </c>
+      <c r="AB23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA24">
+        <v>23</v>
+      </c>
+      <c r="AB24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA25">
+        <v>24</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H22">

--- a/Formulas & Functions/Date-and-Time-Functions/9_Date_Time_Functions_solution.xlsx
+++ b/Formulas & Functions/Date-and-Time-Functions/9_Date_Time_Functions_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Date-and-Time-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBDC6EE-145D-41D1-89C9-F6A0915CEF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3A6255-DC80-4878-A51E-5727363990D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
